--- a/rabbit-web-app/public/sample_excels/dispatch/customer_bulk_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/customer_bulk_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Customers Bulk" sheetId="1" r:id="rId1"/>
+    <sheet name="Customers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,13 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E7"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,7 +413,7 @@
         <v>address</v>
       </c>
       <c r="E1" t="str">
-        <v>pinCode</v>
+        <v>zipCode</v>
       </c>
     </row>
     <row r="2">
@@ -431,7 +424,7 @@
         <v>supplychain@tataconsumer.com</v>
       </c>
       <c r="C2" t="str">
-        <v>+91 22 6665 8282</v>
+        <v>22 6665 8282</v>
       </c>
       <c r="D2" t="str">
         <v>11/13 Botawala Building, Horniman Circle, Fort, Mumbai, Maharashtra</v>
@@ -448,7 +441,7 @@
         <v>orders@unilever.co.in</v>
       </c>
       <c r="C3" t="str">
-        <v>+91 22 3983 0000</v>
+        <v>22 3983 0000</v>
       </c>
       <c r="D3" t="str">
         <v>Unilever House, B. D. Sawant Marg, Chakala, Andheri East, Mumbai</v>
@@ -459,70 +452,70 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nestle India Regional Supply</v>
+        <v>Marico Commercial Cargo</v>
       </c>
       <c r="B4" t="str">
-        <v>commercial@nestle.in</v>
+        <v>logistics@marico.com</v>
       </c>
       <c r="C4" t="str">
-        <v>+91 124 332 1275</v>
+        <v>22 6648 0480</v>
       </c>
       <c r="D4" t="str">
-        <v>Nestle House, Jacaranda Marg, DLF City Phase II, Gurugram, Haryana</v>
+        <v>Grande Palladium, 7th Floor, 175 CST Road, Kalina, Santacruz East, Mumbai</v>
       </c>
       <c r="E4" t="str">
-        <v>122002</v>
+        <v>400098</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ITC FMCG Supply Chain</v>
+        <v>Nestle India Supply Chain</v>
       </c>
       <c r="B5" t="str">
-        <v>procurement@itc.in</v>
+        <v>freight@nestle.in</v>
       </c>
       <c r="C5" t="str">
-        <v>+91 33 2288 9371</v>
+        <v>124 3321275</v>
       </c>
       <c r="D5" t="str">
-        <v>Virginia House, 37 J.L. Nehru Road, Kolkata, West Bengal</v>
+        <v>Nestle House, Jacaranda Marg, M Block, DLF City Phase II, Gurugram</v>
       </c>
       <c r="E5" t="str">
-        <v>700071</v>
+        <v>122002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Marico Consumer Goods</v>
+        <v>Britannia Industries Ltd</v>
       </c>
       <c r="B6" t="str">
-        <v>logistics@marico.com</v>
+        <v>dispatch@britannia.co.in</v>
       </c>
       <c r="C6" t="str">
-        <v>+91 22 6648 0480</v>
+        <v>80 3768 7100</v>
       </c>
       <c r="D6" t="str">
-        <v>Grande Palladium, 7th Floor, 175 CST Road, Kalina, Santacruz East, Mumbai</v>
+        <v>5/1A Hungerford Street, Kolkata, West Bengal</v>
       </c>
       <c r="E6" t="str">
-        <v>400098</v>
+        <v>700017</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Godrej Consumer Products Ltd</v>
+        <v>Dabur India Freight Division</v>
       </c>
       <c r="B7" t="str">
-        <v>corporate.dispatch@godrejcp.com</v>
+        <v>transport@dabur.com</v>
       </c>
       <c r="C7" t="str">
-        <v>+91 22 2518 8010</v>
+        <v>120 3982000</v>
       </c>
       <c r="D7" t="str">
-        <v>Godrej One, Pirojshanagar, Eastern Express Highway, Vikhroli, Mumbai</v>
+        <v>8/3 Asaf Ali Road, New Delhi</v>
       </c>
       <c r="E7" t="str">
-        <v>400079</v>
+        <v>110002</v>
       </c>
     </row>
   </sheetData>
